--- a/data/trans_camb/P57_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Edad-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,99</t>
+          <t>-6,3; 1,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,17</t>
+          <t>-4,17; 5,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,48</t>
+          <t>-4,22; 1,51</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,51; 38,55</t>
+          <t>-84,48; 39,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 93,26</t>
+          <t>-51,12; 105,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 29,22</t>
+          <t>-56,11; 30,99</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,69</t>
+          <t>-9,22; -0,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -1,53</t>
+          <t>-8,69; -1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -2,65</t>
+          <t>-8,3; -2,52</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,91; -4,75</t>
+          <t>-62,62; -4,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,2; -15,91</t>
+          <t>-69,91; -19,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,53; -22,86</t>
+          <t>-60,9; -21,67</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -2,69</t>
+          <t>-10,25; -3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -3,19</t>
+          <t>-10,11; -3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -4,24</t>
+          <t>-9,0; -3,99</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -19,56</t>
+          <t>-61,36; -21,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,05; -25,04</t>
+          <t>-62,96; -28,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,99; -32,48</t>
+          <t>-57,12; -31,03</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,39; -9,64</t>
+          <t>-20,86; -9,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,17; -3,62</t>
+          <t>-12,11; -3,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -8,33</t>
+          <t>-16,31; -7,7</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-83,03; -46,32</t>
+          <t>-84,23; -45,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,78; -18,47</t>
+          <t>-49,47; -19,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-73,02; -40,26</t>
+          <t>-71,07; -38,32</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 6,42</t>
+          <t>-3,6; 6,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -3,3</t>
+          <t>-13,84; -3,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,12</t>
+          <t>-7,49; -0,65</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 38,52</t>
+          <t>-15,75; 38,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -11,71</t>
+          <t>-37,58; -10,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 0,65</t>
+          <t>-25,3; -2,37</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -3,35</t>
+          <t>-14,14; -2,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-33,58; -11,12</t>
+          <t>-34,1; -11,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -9,79</t>
+          <t>-26,16; -9,7</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -13,72</t>
+          <t>-46,41; -11,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,46; -30,65</t>
+          <t>-84,43; -30,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,57; -30,64</t>
+          <t>-72,95; -29,84</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -2,35</t>
+          <t>-17,31; -2,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -8,55</t>
+          <t>-21,42; -7,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,57; -8,15</t>
+          <t>-17,53; -7,64</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,13; -6,54</t>
+          <t>-38,79; -8,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -19,26</t>
+          <t>-39,87; -18,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -18,8</t>
+          <t>-35,85; -18,27</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -3,84</t>
+          <t>-9,03; -4,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -5,58</t>
+          <t>-10,83; -5,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -5,31</t>
+          <t>-9,06; -5,46</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-45,62; -22,16</t>
+          <t>-47,72; -22,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -25,08</t>
+          <t>-45,26; -24,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -26,16</t>
+          <t>-41,21; -26,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_R-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>-1,13</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 1,28</t>
+          <t>-6,34; 1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,07</t>
+          <t>-3,36; 5,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,51</t>
+          <t>-3,65; 1,87</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-46,32%</t>
+          <t>-43,4%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-24,87%</t>
+          <t>-17,4%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,48; 39,29</t>
+          <t>-79,6; 32,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 105,88</t>
+          <t>-44,57; 113,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 30,99</t>
+          <t>-49,71; 35,54</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-4,79</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-3,95</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,24</t>
+          <t>-4,4</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -0,64</t>
+          <t>-9,0; -0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -1,89</t>
+          <t>-7,47; -0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -2,52</t>
+          <t>-7,16; -1,45</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-38,75%</t>
+          <t>-37,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-47,28%</t>
+          <t>-35,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-43,6%</t>
+          <t>-36,66%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,62; -4,12</t>
+          <t>-60,45; -0,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,91; -19,39</t>
+          <t>-58,9; -6,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,9; -21,67</t>
+          <t>-53,65; -13,37</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-6,38</t>
+          <t>-5,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-6,41</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,43</t>
+          <t>-6,17</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -3,02</t>
+          <t>-10,04; -2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -3,44</t>
+          <t>-9,97; -3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -3,99</t>
+          <t>-8,72; -3,73</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-44,29%</t>
+          <t>-41,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-46,62%</t>
+          <t>-46,21%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-45,45%</t>
+          <t>-43,67%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,36; -21,91</t>
+          <t>-59,91; -16,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,96; -28,12</t>
+          <t>-60,71; -28,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; -31,03</t>
+          <t>-55,82; -28,81</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-14,2</t>
+          <t>-11,27</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,33</t>
+          <t>-8,89</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,86; -9,42</t>
+          <t>-15,46; -7,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -3,92</t>
+          <t>-10,86; -2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -7,7</t>
+          <t>-11,86; -5,76</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-65,01%</t>
+          <t>-51,58%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-34,59%</t>
+          <t>-29,86%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-51,46%</t>
+          <t>-40,4%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,23; -45,74</t>
+          <t>-63,58; -35,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -19,79</t>
+          <t>-43,43; -14,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,07; -38,32</t>
+          <t>-49,26; -28,01</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-8,6</t>
+          <t>-8,3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-3,7</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,19</t>
+          <t>-4,49; 5,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -3,36</t>
+          <t>-13,69; -2,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -0,65</t>
+          <t>-7,68; -0,27</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-25,58%</t>
+          <t>-24,7%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-13,75%</t>
+          <t>-13,84%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 38,49</t>
+          <t>-19,2; 34,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,58; -10,79</t>
+          <t>-36,82; -9,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,3; -2,37</t>
+          <t>-26,36; -1,06</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-9,15</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-21,5</t>
+          <t>-13,11</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-15,68</t>
+          <t>-11,34</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -2,52</t>
+          <t>-14,73; -3,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-34,1; -11,43</t>
+          <t>-19,01; -7,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,16; -9,7</t>
+          <t>-15,25; -7,16</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-31,51%</t>
+          <t>-33,42%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-56,48%</t>
+          <t>-34,44%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-47,41%</t>
+          <t>-34,29%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,41; -11,34</t>
+          <t>-47,14; -15,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,43; -30,85</t>
+          <t>-45,11; -22,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,95; -29,84</t>
+          <t>-42,82; -24,25</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-9,7</t>
+          <t>-10,15</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-14,46</t>
+          <t>-14,34</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,62</t>
+          <t>-12,73</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,31; -2,93</t>
+          <t>-16,72; -3,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -7,92</t>
+          <t>-20,94; -7,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,53; -7,64</t>
+          <t>-17,54; -7,95</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-23,9%</t>
+          <t>-25,01%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-29,61%</t>
+          <t>-29,36%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-27,68%</t>
+          <t>-27,92%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-38,79; -8,14</t>
+          <t>-37,86; -8,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,87; -18,15</t>
+          <t>-39,41; -17,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -18,27</t>
+          <t>-35,78; -18,65</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-6,06</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-7,7</t>
+          <t>-6,18</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,65</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -4,03</t>
+          <t>-7,0; -3,31</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -5,58</t>
+          <t>-8,11; -4,28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -5,46</t>
+          <t>-6,9; -4,46</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-32,71%</t>
+          <t>-27,66%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-32,82%</t>
+          <t>-26,32%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-26,85%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -22,9</t>
+          <t>-35,2; -18,41</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-45,26; -24,65</t>
+          <t>-33,17; -19,49</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -26,63</t>
+          <t>-32,08; -21,9</t>
         </is>
       </c>
     </row>
